--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3576,8 +3576,74 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Internal Doors_interior door_wooden door</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>8613858903277</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>sales@kkdgroup.com</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kkddoors.com/</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>armored door supplier south africa kenya</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Carbon Steel in Door Manufacturing: A Comprehensive B2B Guide</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>046097825, 649156247, 820704331</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr"/>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>https://seller.alibaba.com/blogs/2026/southeast-asia/doors-windows/carbon-steel-</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>site:alibaba.com steel door africa importer</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G97"/>
+  <autoFilter ref="A1:G99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3642,8 +3642,136 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Steel door manufacturer Istanbul</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>عام</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>1978100199, 1997200499, 2004100199, 2018200499, 5075100125</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr"/>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.europages.co.uk/companies/city-istanbul/steel-door-manufacturer.html</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>best steel door manufacturer istanbul</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>FIRE DOORS</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>217014566</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>sales@amdoor.co.za</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amdoor.co.za/fire-doors</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>fire door distributor senegal ivory coast</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>An Introduction To Fire Doors</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>0683054568, 27683054568</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>https://doorsonline.co.za/fire-doors/</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>fire door distributor senegal ivory coast</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Metal Doors &amp; Frames</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>57701605341</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>https://commercialdoorinc.com/metal-doors-frames/</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>metal door importer tanzania ethiopia</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G99"/>
+  <autoFilter ref="A1:G103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$104</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3770,8 +3770,43 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Steel Security Door Importers</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>مصر</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>01227286000, 201223341595, 247078685, 381943312, 38345553928, 772470391, 820637064</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>eg.sample@xyz.com, madi1962@gmail.com</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>https://importer.tradekey.com/steel-security-door-importer.html</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>steel door importer egypt</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G103"/>
+  <autoFilter ref="A1:G104"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$105</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3805,8 +3805,39 @@
         </is>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>door turkey suppliers</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>عام</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>010177216133</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr"/>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.alibaba.com/door-turkey-suppliers.html</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>steel door turkey supplier whatsapp</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G104"/>
+  <autoFilter ref="A1:G105"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$109</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3902,8 +3902,78 @@
         </is>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>BLINDEES - 36 Annonces</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>المغرب</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>212613747656, 212662150999, 32475237232, 5307721135, 8615831127175, 892430890, 903523114888, 903523213708, 903523221915, 905077523234, 905307721135, 905321346970, 905321686950, 905352832, 905372632885, 905424088616, 905533346136, 905545334550</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>senol@demir.eu</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.algomtl.com/acheter/recherche-fournisseur-0-blindees.html</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>porte blindee maroc import turquie</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>شركة زان لإستيراد الابواب المصفحة</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>مصر</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>01111555129, 011115551290111</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>info@zan-eg.com</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>https://zan-eg.com/</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>وكيل باب مصفح تركي في مصر</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G107"/>
+  <autoFilter ref="A1:G109"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$115</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4038,8 +4038,136 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Leading Steel Door Suppliers in India</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>عام</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>919072101088</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>kinzasteeldoors@gmail.com</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>https://kinzasteeldoor.com/</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>best steel door manufacturer istanbul</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Petra Steel Doors &amp; Windows</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>عام</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>91623801188, 91859060262, 91907270444</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr"/>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.petradoor.com/</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>best steel door manufacturer istanbul</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Steel Door Turkey Manufacturers &amp; Suppliers</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>عام</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>201202304410, 201304304, 315011000</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr"/>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.Made-in-China.com/manufacturers/steel-door-turkey.html</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>wholesale steel door turkey exporter</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>الاعلانات المدللة ب 'صناعة تركية' (41)</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>الاردن</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>905453215658</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr"/>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>https://sharray.net/ad-tag/صناعة-تركية/</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>شركة ابواب تركية الاردن</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G111"/>
+  <autoFilter ref="A1:G115"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$116</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4166,8 +4166,39 @@
         </is>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Free Search List of Importers &amp; Buyers Globally</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>919667735607</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr"/>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.seair.co.in/steel-door-importers</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>steel door importer ghana nigeria kenya</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G115"/>
+  <autoFilter ref="A1:G116"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$118</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4197,8 +4197,74 @@
         </is>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>SECURITY SOLUTIONS YOU CAN TRUST</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>0860333363</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr"/>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>https://defendoor.co.za/</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>armored door supplier south africa kenya</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Steel doors in Agadir Morocco</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>المغرب</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>01968671681</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>info@directdoors.com</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.directdoors.com/blogs/news/steel-doors-agadir-morocco</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>steel door importer morocco</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G116"/>
+  <autoFilter ref="A1:G118"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$120</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4263,8 +4263,74 @@
         </is>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Africa Security Doors and Frame Single Iron Stainless Steel Office Front Door</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>7308300000</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr"/>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>https://eagledoor.en.made-in-china.com/product/BOJTWegZXuUY/China-Africa-Securit</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>safety door supplier west africa</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Avansa Security Doors - Security Doors for Sale</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>27870953333</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>sales@avansa.co.za, security@avansa.co.za</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>https://avansa.co.za/collections/security-doors?srsltid=AfmBOooHjVTWIujZuZMhZ-_Z</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>safety door supplier west africa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G118"/>
+  <autoFilter ref="A1:G120"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$121</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4329,8 +4329,43 @@
         </is>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Fire rated front doors residential in Egypt - Best Price - Star Light</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>مصر</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>01220348885, 012203488850222, 02267106650122</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>info@starlight-egy.com, khaledelmesedy@starlight-egy.com, nasserelmsidy@starlight-egy.com</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>https://starlight-egy.com/steel-doors/</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>steel door importer egypt</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G120"/>
+  <autoFilter ref="A1:G121"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$124</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4399,8 +4399,78 @@
         </is>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Door Supplier in Nigeria – Buy HDF and Steel Doors</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>08148576051</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>sales@goltava.com</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>https://goltava.com/product/door-supplier-in-nigeria-buy-hdf-and-steel-doors/</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>metal door dealer ghana nigeria cameroon</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Best stainless steel doors Nigeriastainless steel doors Nigeria suppliersstain</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>86075785619697, 8618688202143</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>lily@cngrandsea.com</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cngrandsea.com/stainless-steel-doors-nigeria_sp_2</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>metal door dealer ghana nigeria cameroon</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G122"/>
+  <autoFilter ref="A1:G124"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$126</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G124"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4469,8 +4469,74 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Top Steel Door Manufacturers</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>عام</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>91780193869, 91851168556</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>jcfiredoor@gmail.com</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>https://jcfiredoor.com/top-steel-door-manufacturers/</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>best steel door manufacturer istanbul</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>ابواب خارجية حديد للبيع‏(14)</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>العراق</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>077031494, 077032063, 077032187, 077054260, 077080064, 077111411, 077131301, 077135729, 077136565, 077137771, 077159496, 077225329, 077236639, 077266399, 077318338, 077326873, 077394698, 077486481, 077625953, 077626129, 077674358, 078021933, 078477415</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr"/>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>https://iq.opensooq.com/ar/tags/ابواب-خارجية-حديد-للبيع</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>ابواب حديد بغداد</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G124"/>
+  <autoFilter ref="A1:G126"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G126"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4535,8 +4535,43 @@
         </is>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Specialty Doors &amp; Frames</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>الاردن</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>18668482667, 20962632851891, 8668482667, 940051010888, 953416404888, 953416406</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>info@titanmetalproducts.com</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>https://titanmetalproducts.com/</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>steel door importer jordan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G126"/>
+  <autoFilter ref="A1:G127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$128</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4570,8 +4570,43 @@
         </is>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Security Doors Importers</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>الاردن</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>01227286000, 3244177250, 38345553928, 545975179, 9383478540</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>eg.sample@xyz.com</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>https://importer.tradekey.com/security-doors-importer.html</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>steel door importer jordan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G127"/>
+  <autoFilter ref="A1:G128"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$129</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4605,8 +4605,39 @@
         </is>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Safety and Homesolutions</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>233270766662</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr"/>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sahsghana.com/?srsltid=AfmBOoq34505q5yZgmOj6eHhqgIQT12gqjT-pPWfXVPrc</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>safety door supplier west africa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G128"/>
+  <autoFilter ref="A1:G129"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$133</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G132"/>
+  <dimension ref="A1:G133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4737,8 +4737,39 @@
         </is>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>steel door</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>عام</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>91868607216</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr"/>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>https://globaltradeplaza.com/product/steel-door-10</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>wholesale steel door turkey exporter</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G132"/>
+  <autoFilter ref="A1:G133"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$135</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G134"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4799,8 +4799,39 @@
         </is>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>New Turkey Design Exterior Security Steel Door.</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>عام</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>730830000</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr"/>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>https://sfdoors.en.made-in-china.com/product/XALYrolWhdVa/China-New-Turkey-Desig</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>wholesale steel door turkey exporter</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G134"/>
+  <autoFilter ref="A1:G135"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$136</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G135"/>
+  <dimension ref="A1:G136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4830,8 +4830,43 @@
         </is>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Doors Kenya</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>254711752452</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>info@doors.co.ke</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>https://doors.co.ke/index.html</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>armored door supplier south africa kenya</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G135"/>
+  <autoFilter ref="A1:G136"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$138</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G137"/>
+  <dimension ref="A1:G138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4900,8 +4900,39 @@
         </is>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>100620251088, 100620251090, 1024202501, 10242025010, 10242025014, 10242025016, 1024202502, 10242025022, 10242025023, 10242025024, 1024202504, 1024202506, 1024202507, 1024202509, 1111202502, 1111202506, 2204253985, 2204253986, 2204253987, 2304253980, 2310202504, 2310202506, 2310202508, 23768047794, 2410202509</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr"/>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>https://maimo.cm/index.php/home/doors.html</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>metal door dealer ghana nigeria cameroon</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G137"/>
+  <autoFilter ref="A1:G138"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$142</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G140"/>
+  <dimension ref="A1:G142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4997,8 +4997,78 @@
         </is>
       </c>
     </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Pyropanel Fire Doors</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>27315737380, 27315737381, 27826527667</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>gtgsales@ifuba.co.za, info@ifuba.co.za</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ifuba.co.za/pyropanel-fire-doors/</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>fire door distributor senegal ivory coast</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Fully compliant quality fire doors brought to you with the shortest industry le</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>0607715599</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>info@crisisfiredoors.co.za</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>https://crisisfiredoors.co.za/</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>fire door distributor senegal ivory coast</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G140"/>
+  <autoFilter ref="A1:G142"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$144</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G142"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5067,8 +5067,70 @@
         </is>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>New Model Egypt 3 Panel Design Steel Security Door</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>مصر</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>129552008, 6000200299, 7308300000</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr"/>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>https://haojundoor.en.made-in-china.com/product/XjEmVPFCLRks/China-New-Model-Egy</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>steel door importer egypt</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Creative Solutions.Innovative Designs.Proven Products.</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>8002669392</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr"/>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mckeondoor.com/</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>fire door distributor senegal ivory coast</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G142"/>
+  <autoFilter ref="A1:G144"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$147</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G144"/>
+  <dimension ref="A1:G147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5129,8 +5129,101 @@
         </is>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>steel door in turkey suppliers</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>عام</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>011008085013</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr"/>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.alibaba.com/steel-door-in-turkey-suppliers.html</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>steel door turkey supplier whatsapp</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>STEEL DOORS</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>2348032254136</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr"/>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sabasteelng.com/products/steel-doors/</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>steel door importer ghana nigeria kenya</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>Steel door importers Turkey</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>ليبيا</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>1979100199, 1997200499, 2000100199, 5075100125</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr"/>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.europages.co.uk/companies/turkey/steel-door-importers.html</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>steel door importer libya</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G144"/>
+  <autoFilter ref="A1:G147"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$149</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$150</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G149"/>
+  <dimension ref="A1:G150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5284,8 +5284,43 @@
         </is>
       </c>
     </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Customers Visit USELUCK Steel Door Factory After Canton Fair Success</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>عام</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>8615355074999</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>sales01@useluckdoor.com</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>https://spa.useluckdoor.com/a/customers-visit-useluck-steel-door-factory-after-c</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>steel door factory turkey contact</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G149"/>
+  <autoFilter ref="A1:G150"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$151</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G150"/>
+  <dimension ref="A1:G151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5319,8 +5319,39 @@
         </is>
       </c>
     </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>Imported Steel Doors Single</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>0748333000</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr"/>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>https://wajenzistores.com/product/imported-steel-doors-single/</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>steel door importer ghana nigeria kenya</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G150"/>
+  <autoFilter ref="A1:G151"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$151</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$152</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G151"/>
+  <dimension ref="A1:G152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5350,8 +5350,43 @@
         </is>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Metal Doors Importers</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>381943312, 858886866</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>eg.sample@xyz.com</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>https://importer.tradekey.com/metal-doors-importer.html</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>metal door importer tanzania ethiopia</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G151"/>
+  <autoFilter ref="A1:G152"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$153</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G152"/>
+  <dimension ref="A1:G153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5385,8 +5385,39 @@
         </is>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>Africa Armored Steel Wooden Medium Africa Steel Wooden Door Armored Steel Securi</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>5800100199, 7610100000</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr"/>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>https://hendawindow.en.made-in-china.com/product/lwNtdVrAHLpx/China-Africa-Armor</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>armored door supplier south africa kenya</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G152"/>
+  <autoFilter ref="A1:G153"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$153</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$154</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G153"/>
+  <dimension ref="A1:G154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5416,8 +5416,43 @@
         </is>
       </c>
     </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Doors Kenya - Cemmax Building Supplies ltd</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>0716704836, 0722243028</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>info@cemmaxsupplies.co.ke</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>https://cemmaxsupplies.co.ke/product-category/doors-kenya/</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>armored door supplier south africa kenya</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G153"/>
+  <autoFilter ref="A1:G154"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$154</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$155</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G154"/>
+  <dimension ref="A1:G155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5451,8 +5451,39 @@
         </is>
       </c>
     </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>Premium Steel Doors for Modern Living</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>201222168014</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr"/>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.marinadoors.com/</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>armored door supplier south africa kenya</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G154"/>
+  <autoFilter ref="A1:G155"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$155</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$159</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G155"/>
+  <dimension ref="A1:G159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5482,8 +5482,148 @@
         </is>
       </c>
     </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Nigeria Doors Buyers Importers Distributors Wholesale agents and Resellers re</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>2348120407404, 2348162236155</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>eg.sample@xyz.com</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>https://importer.tradekey.com/nigeria/doors.htm</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>steel door importer ghana nigeria kenya</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Tendi Security Group</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>233249895959, 23790590687, 255714890000, 255787696932, 260966637641, 260979491093, 263711421139, 263771714424, 263772431152, 26771537096, 26771884124, 26776478727, 27738124650, 4915774427144</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>accounts.bw@ttsg.africa, accounts.zm@ttsg.africa, accounts.zw@ttsg.africa, chama@ttsg.africa, cyrille.avebe@ttsg.africa, dimitri@ttsg.africa, emmanuel.engoulou@ttsg.africa, hector@ttsg.africa, kojo.assempah@ttsg.africa, kuda@ttsg.africa, michael@ehs.co.tz, sales.bw@ttsg.africa, sales.cm@ttsg.africa, sales.de@ttsg.africa, sales.gh@ttsg.africa, sales.mw@ttsg.africa, sales.tz@ttsg.africa, sales.za@ttsg.africa, sales.zm@ttsg.africa, sales.zw@ttsg.africa</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>https://ttsg.africa/web/</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>safety door supplier west africa</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>China Building Materials Supplier</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>عام</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>8619183969627</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>hailongyan@snrida.com</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.snrida.com/</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>steel door factory turkey contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>China Wanxin Group</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>عام</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>8613868928, 865798299</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>sunny@chinawanxin.com</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>http://chinawanxin.com/</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>steel door factory turkey contact</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G155"/>
+  <autoFilter ref="A1:G159"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$159</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$160</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G159"/>
+  <dimension ref="A1:G160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5622,8 +5622,43 @@
         </is>
       </c>
     </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Company Profile</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>199820012006, 200820162018, 254711752452</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>info@doors.co.ke</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>https://doors.co.ke/company-profile/index.html</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>armored door supplier south africa kenya</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G159"/>
+  <autoFilter ref="A1:G160"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$160</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$162</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G160"/>
+  <dimension ref="A1:G162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5657,8 +5657,74 @@
         </is>
       </c>
     </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>Steel Doors Exporters Suppliers &amp; Manufacturers in Turkey</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>عام</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>201304316430</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>eg.sample@xyz.com</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>https://turkey.tradekey.com/steel-doors.htm</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>wholesale steel door turkey exporter</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>أبواب وإكسسوارات أبواب للبيع في العراق‏(227)</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>العراق</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>077064187, 077070708, 077070909, 077112010, 077122141, 077124236, 077124730, 077150375, 077152800, 077181834, 077182671, 077320422, 077321966, 077324645, 077353972, 077448417, 077525647, 077709689, 077837871, 078066820, 078161715, 078262110, 078318865, 078332233, 078588296, 078760893, 079011667</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr"/>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>https://iq.opensooq.com/ar/المنزل-والحديقة/أبواب-وإكسسوارات-الأبواب</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>معرض ابواب في العراق</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G160"/>
+  <autoFilter ref="A1:G162"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$162</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$163</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G162"/>
+  <dimension ref="A1:G163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5723,8 +5723,43 @@
         </is>
       </c>
     </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>Exterior Steel Door Importers</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>مصر</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>38345553928</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>eg.sample@xyz.com</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>https://importer.tradekey.com/exterior-steel-door-importer.html</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>steel door importer egypt</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G162"/>
+  <autoFilter ref="A1:G163"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$163</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$167</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G163"/>
+  <dimension ref="A1:G167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5758,8 +5758,136 @@
         </is>
       </c>
     </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>اسعار الابواب المصفحة فى مصر</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>العراق</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>201044545111, 966594697944</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>info@htcsafety.com</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>https://htcsafety.com/اسعار-الابواب-المصفحة-فى-مصر/</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>اسعار الابواب المصفحة في العراق</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Ivory Coast Fire Rated Glass Solutions – Certified for Local Building Safety</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>120120120</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr"/>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>https://antifires.com/fire_rated_glass/Ivory_Coast/en/</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>fire door distributor senegal ivory coast</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>أبواب ونوافذ    للبيع في  المغرب : 2047 إعلانات</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>المغرب</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>0674453693</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr"/>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.avito.ma/ar/خريبكة/أبواب_ونوافذ/ابواب_تركية_مصفحة_56347766.htm</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>ابواب مصفحة من تركيا المغرب واتس</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Steel Door Turkey Manufacturers &amp; Suppliers</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>عام</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>201202304410, 201304304, 335011000</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr"/>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.made-in-china.com/manufacturers/steel-door-turkey.html</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>wholesale steel door turkey exporter</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G163"/>
+  <autoFilter ref="A1:G167"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$167</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$168</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G167"/>
+  <dimension ref="A1:G168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5886,8 +5886,39 @@
         </is>
       </c>
     </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Certified Fire Rated Doors &amp; Emergency Exit Doors – Egypt</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>مصر</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>201039713471, 238340300</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr"/>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>https://beta-metal.com/</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>steel door importer egypt</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G167"/>
+  <autoFilter ref="A1:G168"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$168</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$169</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G168"/>
+  <dimension ref="A1:G169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5917,8 +5917,43 @@
         </is>
       </c>
     </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>DurableQuality Products</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>254705656565, 254721892764, 905326311375</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>hello@eurodoor.co.ke</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.eurodoor.co.ke/</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>armored door supplier south africa kenya</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G168"/>
+  <autoFilter ref="A1:G169"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$170</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G169"/>
+  <dimension ref="A1:G170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5952,8 +5952,43 @@
         </is>
       </c>
     </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Steel Doors</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>عام</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>05336516539, 903123853783</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>ack@ankaracelikkapi.com.tr</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>https://ankaracelikkapi.com.tr/en</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>best steel door manufacturer istanbul</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G169"/>
+  <autoFilter ref="A1:G170"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$170</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$172</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G170"/>
+  <dimension ref="A1:G172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5987,8 +5987,74 @@
         </is>
       </c>
     </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>Fire Rated</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>8557699895</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>sales@cdfdistributors.com, sales@cdfdoors.com</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cdfdistributors.com/doors/specialty-doors/fire-rated</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>fire door distributor senegal ivory coast</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>Certified Fire Doors.Engineered for Safety. Built for Compliance.</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>27210023333</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr"/>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dorwerx.co.za/</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>fire door distributor senegal ivory coast</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G170"/>
+  <autoFilter ref="A1:G172"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$172</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$173</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G172"/>
+  <dimension ref="A1:G173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6053,8 +6053,43 @@
         </is>
       </c>
     </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>Imported steel doors. 70mm thick 2200*1200mm - Construction Revolution Market</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>254734773843</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>info@crmkenya.com</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>https://www.crmkenya.com/product/482</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>steel door importer ghana nigeria kenya</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G172"/>
+  <autoFilter ref="A1:G173"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$174</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G173"/>
+  <dimension ref="A1:G174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6088,8 +6088,43 @@
         </is>
       </c>
     </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Steel Doors Importers</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>27833895606</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>eg.sample@xyz.com</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>https://importer.tradekey.com/steel-doors-importer.html</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>steel door importer ghana nigeria kenya</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G173"/>
+  <autoFilter ref="A1:G174"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$174</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G174"/>
+  <dimension ref="A1:G175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6123,8 +6123,39 @@
         </is>
       </c>
     </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>Fire Doors</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>عام</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>1978100199, 2003100199, 2005100199, 5075100125</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr"/>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>https://www.europages.co.uk/companies/pg-4/fire+doors.html</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>steel door turkey supplier whatsapp</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G174"/>
+  <autoFilter ref="A1:G175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$177</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G175"/>
+  <dimension ref="A1:G177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6154,8 +6154,70 @@
         </is>
       </c>
     </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Wholesale Steel Doors from Turkey - Factory Direct Prices - Özkuvvet</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>عام</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>05496858095, 8691311000111</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr"/>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>https://ozkuvvet.com/wholesale-steel-doors-from-turkey-factory-direct-prices-ozk</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>wholesale steel door turkey exporter</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>Turkey Kayseri</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>عام</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>1973200499, 2005100199, 2012100199, 5075100125</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr"/>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>https://www.europages.co.uk/companies/city-kayseri/turkey.html</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>steel door turkey supplier whatsapp</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G175"/>
+  <autoFilter ref="A1:G177"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$178</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G177"/>
+  <dimension ref="A1:G178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6216,8 +6216,43 @@
         </is>
       </c>
     </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>Metal Door Importers</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>1000000000, 381943312, 858886866</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>eg.sample@xyz.com</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>https://importer.tradekey.com/metal-door-importer.html</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>metal door importer tanzania ethiopia</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G177"/>
+  <autoFilter ref="A1:G178"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$179</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G178"/>
+  <dimension ref="A1:G179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6251,8 +6251,44 @@
         </is>
       </c>
     </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>Global Architectural
+Door Systems</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>عام</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>8613126008852</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>cyxs001@gmail.com</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>https://doorwoodendoors.com/</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>steel door factory turkey contact</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G178"/>
+  <autoFilter ref="A1:G179"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$180</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G179"/>
+  <dimension ref="A1:G180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6287,8 +6287,43 @@
         </is>
       </c>
     </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Doors &amp;HardwareSimplified</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>8443213667, 902483100</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>sales@usafiredoor.com</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.usafiredoor.com/</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>fire door distributor senegal ivory coast</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G179"/>
+  <autoFilter ref="A1:G180"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$181</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G180"/>
+  <dimension ref="A1:G181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6322,8 +6322,39 @@
         </is>
       </c>
     </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>Fire doors Turkey</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>عام</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>1978100199, 2001200499, 2003100199, 2005100199, 5075100125</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr"/>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.europages.co.uk/companies/turkey/fire-doors.html</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>steel door turkey supplier whatsapp</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G180"/>
+  <autoFilter ref="A1:G181"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$182</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G181"/>
+  <dimension ref="A1:G182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6353,8 +6353,39 @@
         </is>
       </c>
     </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>أبواب ونوافذ للبيع في مصر‏(62)</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>مصر</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>010005659, 010013283, 010021911, 010051109, 010056666, 010056990, 010062738, 010269913, 010331668, 010367247, 010500745, 010938115, 011166456, 011195508, 011421594, 011581172, 012024029, 012231775, 012244660, 012258390, 012270050, 012842955, 012880586, 015518334, 015557047</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr"/>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>https://eg.opensooq.com/ar/المنزل-والحديقة/أبواب-شباببيك-ألمنيوم</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>site:opensooq.com ابواب مصفحة مصر</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G181"/>
+  <autoFilter ref="A1:G182"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$184</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G182"/>
+  <dimension ref="A1:G184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6384,8 +6384,70 @@
         </is>
       </c>
     </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>Collection:Internal Doors</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>01429241270, 434778464</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr"/>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.leaderdoors.co.uk/doors-c14/internal-doors-c111</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>fire door distributor senegal ivory coast</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>ابواب امان</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>الاردن</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>905541523599</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr"/>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.adwhit.com/ar/ابواب-امان-366291</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>باب امان تركي الاردن معارض</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G182"/>
+  <autoFilter ref="A1:G184"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$184</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$185</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G184"/>
+  <dimension ref="A1:G185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6446,8 +6446,43 @@
         </is>
       </c>
     </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>Quality &amp; Safety is YSE TOP PRIORITY!</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>0378472292, 60378472292, 60378472522</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>info@yse.com.my</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>https://securitydoor.com.my/</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>safety door supplier west africa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G184"/>
+  <autoFilter ref="A1:G185"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$186</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G185"/>
+  <dimension ref="A1:G186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6481,8 +6481,39 @@
         </is>
       </c>
     </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>steel+door+importers</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>ليبيا</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>1909100199, 1959200499, 1969100199, 2000100199, 2015100199, 5075100125</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr"/>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.europages.co.uk/companies/steel+door+importers.html</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>steel door importer libya</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G185"/>
+  <autoFilter ref="A1:G186"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$187</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G186"/>
+  <dimension ref="A1:G187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6512,8 +6512,39 @@
         </is>
       </c>
     </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>Best Steel Security Doors in Kenya 2025</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>0701410647, 2540701410647</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr"/>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>https://dooritdoorsplus.co.ke/best-steel-security-doors-in-kenya-2025-why-homeow</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>armored door supplier south africa kenya</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G186"/>
+  <autoFilter ref="A1:G187"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$189</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G187"/>
+  <dimension ref="A1:G189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6543,8 +6543,74 @@
         </is>
       </c>
     </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>₦airaland Forum</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>07062764235</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>roofanddoorimporter@yahoo.com, wholesaleroofingsheetanddoors@yahoo.co.uk</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nairaland.com/1243181/mr-donald-roof-doors-importer</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>steel door importer ghana nigeria kenya</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>Steel_door Buyers</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>1115674111, 2348137914588, 84909766895, 982133112367, 982133994885, 989123943577</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr"/>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>https://importer.ec21.com/steel_door.html</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>steel door importer ghana nigeria kenya</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G187"/>
+  <autoFilter ref="A1:G189"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$189</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$190</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G189"/>
+  <dimension ref="A1:G190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6609,8 +6609,39 @@
         </is>
       </c>
     </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>Double Bolt Rim Door Lock</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>2020120140</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr"/>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>https://www.alibaba.com/showroom/double-bolt-rim-door-lock.html</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>site:alibaba.com steel door africa importer</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G189"/>
+  <autoFilter ref="A1:G190"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$190</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$192</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G190"/>
+  <dimension ref="A1:G192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6640,8 +6640,70 @@
         </is>
       </c>
     </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>How to Choose Turkish Security Doors: A Complete Buying Guide</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>عام</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>220120091, 33010002000092</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr"/>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>https://smartbuy.alibaba.com/buyingguides/turkish-security-doors</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>site:alibaba.com steel security door turkey</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>High-Security Solutions for Retail Stores and Showrooms</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>18552232069</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr"/>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>https://www.armored-doors.com/</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>armored door supplier south africa kenya</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G190"/>
+  <autoFilter ref="A1:G192"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$193</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G192"/>
+  <dimension ref="A1:G193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6702,8 +6702,39 @@
         </is>
       </c>
     </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>"Steel Door Turkey"</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>عام</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>0201304316</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr"/>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>https://www.made-in-china.com/products-search/hot-china-products/Steel_Door_Turk</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>wholesale steel door turkey exporter</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G192"/>
+  <autoFilter ref="A1:G193"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$194</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G193"/>
+  <dimension ref="A1:G194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6733,8 +6733,43 @@
         </is>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>Panel Steel Door Exporters Suppliers &amp; Manufacturers in Turkey</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>عام</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>201606170615085</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>eg.sample@xyz.com</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>https://www.tradekey.com/turkey/panel-steel-door.html</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>wholesale steel door turkey exporter</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G193"/>
+  <autoFilter ref="A1:G194"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$194</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$195</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G194"/>
+  <dimension ref="A1:G195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6768,8 +6768,39 @@
         </is>
       </c>
     </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>Steel door importers Italy</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>الاردن</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>5075100125</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr"/>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>https://www.europages.co.uk/companies/italy/steel-door-importers.html</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>steel door importer jordan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G194"/>
+  <autoFilter ref="A1:G195"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$195</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$196</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G195"/>
+  <dimension ref="A1:G196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6799,8 +6799,39 @@
         </is>
       </c>
     </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>KARTELA STEEL DOOR FACTORY</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>عام</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>905068821144</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr"/>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>https://www.europages.co.uk/KARTELA-STEEL-DOOR-FACTORY/00000005269574-583365001.</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>steel door factory turkey contact</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G195"/>
+  <autoFilter ref="A1:G196"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$196</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$197</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G196"/>
+  <dimension ref="A1:G197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6830,8 +6830,39 @@
         </is>
       </c>
     </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>Find Verified Doors Suppliers Manufacturers and Wholesalers</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>الاردن</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>16469128384, 1800114649, 18337527161, 911141507600, 91892980077</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr"/>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>https://www.go4worldbusiness.com/suppliers/jordan/doors.html</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>steel door importer jordan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G196"/>
+  <autoFilter ref="A1:G197"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>